--- a/data/trans_camb/P38A-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/P38A-Habitat-trans_camb.xlsx
@@ -631,32 +631,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-5,88; 1,32</t>
+          <t>-5,87; 0,95</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-2,56; 5,7</t>
+          <t>-3,62; 5,41</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-2,77; 3,9</t>
+          <t>-2,33; 4,29</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1,09; 7,04</t>
+          <t>1,1; 7,31</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-3,34; 1,58</t>
+          <t>-3,36; 1,77</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,16; 5,41</t>
+          <t>0,26; 5,78</t>
         </is>
       </c>
     </row>
@@ -707,32 +707,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-6,65; 1,54</t>
+          <t>-6,58; 1,1</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-2,85; 6,59</t>
+          <t>-4,04; 6,24</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-3,04; 4,47</t>
+          <t>-2,56; 4,98</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1,23; 8,09</t>
+          <t>1,25; 8,61</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-3,75; 1,81</t>
+          <t>-3,75; 2,03</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,17; 6,18</t>
+          <t>0,3; 6,69</t>
         </is>
       </c>
     </row>
@@ -787,32 +787,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-3,76; 3,02</t>
+          <t>-4,04; 3,1</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-45,56; 0,61</t>
+          <t>-50,9; 0,57</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,36; 6,43</t>
+          <t>1,31; 6,41</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-2,92; 3,05</t>
+          <t>-2,78; 3,0</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-0,57; 4,11</t>
+          <t>-0,54; 3,84</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-35,44; 0,65</t>
+          <t>-35,09; 0,5</t>
         </is>
       </c>
     </row>
@@ -863,32 +863,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-4,46; 3,7</t>
+          <t>-4,76; 3,86</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-55,54; 0,72</t>
+          <t>-60,95; 0,69</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,53; 7,44</t>
+          <t>1,46; 7,44</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-3,24; 3,51</t>
+          <t>-3,07; 3,43</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-0,67; 4,85</t>
+          <t>-0,63; 4,52</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-40,84; 0,72</t>
+          <t>-40,55; 0,61</t>
         </is>
       </c>
     </row>
@@ -943,32 +943,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-5,78; 2,35</t>
+          <t>-5,51; 1,91</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-6,91; 2,89</t>
+          <t>-6,82; 2,87</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-1,84; 4,22</t>
+          <t>-1,98; 3,79</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-1,53; 6,55</t>
+          <t>-1,46; 7,16</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-2,86; 2,11</t>
+          <t>-2,91; 2,09</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-2,39; 5,06</t>
+          <t>-2,37; 5,66</t>
         </is>
       </c>
     </row>
@@ -1019,32 +1019,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-6,65; 2,85</t>
+          <t>-6,37; 2,14</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-7,89; 3,47</t>
+          <t>-7,93; 3,43</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-2,0; 4,79</t>
+          <t>-2,18; 4,24</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-1,73; 7,42</t>
+          <t>-1,65; 8,02</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-3,21; 2,45</t>
+          <t>-3,3; 2,43</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-2,72; 5,79</t>
+          <t>-2,67; 6,5</t>
         </is>
       </c>
     </row>
@@ -1099,32 +1099,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-5,87; 0,7</t>
+          <t>-5,97; 0,76</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-9,39; -1,56</t>
+          <t>-9,75; -2,11</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-7,29; -1,5</t>
+          <t>-7,23; -1,5</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-25,7; -3,14</t>
+          <t>-24,52; -2,7</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-5,66; -1,17</t>
+          <t>-5,86; -1,4</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-19,04; -3,87</t>
+          <t>-17,31; -3,84</t>
         </is>
       </c>
     </row>
@@ -1175,32 +1175,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-6,72; 0,81</t>
+          <t>-6,87; 0,91</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-10,77; -1,83</t>
+          <t>-11,18; -2,52</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-7,95; -1,69</t>
+          <t>-7,86; -1,67</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-28,58; -3,51</t>
+          <t>-26,86; -2,99</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-6,39; -1,35</t>
+          <t>-6,55; -1,61</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-21,71; -4,43</t>
+          <t>-19,35; -4,31</t>
         </is>
       </c>
     </row>
@@ -1255,32 +1255,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-3,49; 0,11</t>
+          <t>-3,55; 0,03</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-24,37; -0,99</t>
+          <t>-25,32; -1,13</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-1,34; 1,6</t>
+          <t>-1,36; 1,65</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-8,07; 1,06</t>
+          <t>-7,16; 1,1</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-1,91; 0,37</t>
+          <t>-1,83; 0,36</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-14,0; -0,63</t>
+          <t>-14,12; -0,77</t>
         </is>
       </c>
     </row>
@@ -1331,32 +1331,32 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-4,06; 0,14</t>
+          <t>-4,12; 0,03</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-28,58; -1,16</t>
+          <t>-29,6; -1,35</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-1,48; 1,81</t>
+          <t>-1,5; 1,85</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-8,98; 1,18</t>
+          <t>-7,99; 1,22</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-2,16; 0,43</t>
+          <t>-2,08; 0,41</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-15,94; -0,73</t>
+          <t>-16,3; -0,9</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P38A-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/P38A-Habitat-trans_camb.xlsx
@@ -598,7 +598,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>2,03</t>
+          <t>1,46</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -608,7 +608,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>3,98</t>
+          <t>3,06</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -618,7 +618,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,05</t>
+          <t>2,31</t>
         </is>
       </c>
     </row>
@@ -631,32 +631,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-5,87; 0,95</t>
+          <t>-6,33; 1,4</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-3,62; 5,41</t>
+          <t>-2,68; 5,3</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-2,33; 4,29</t>
+          <t>-2,56; 4,25</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1,1; 7,31</t>
+          <t>0,09; 6,12</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-3,36; 1,77</t>
+          <t>-3,37; 1,94</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,26; 5,78</t>
+          <t>-0,23; 5,03</t>
         </is>
       </c>
     </row>
@@ -674,7 +674,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>4,47%</t>
+          <t>3,44%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -694,7 +694,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>2,61%</t>
         </is>
       </c>
     </row>
@@ -707,32 +707,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-6,58; 1,1</t>
+          <t>-7,05; 1,63</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-4,04; 6,24</t>
+          <t>-2,96; 6,17</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-2,56; 4,98</t>
+          <t>-2,83; 4,87</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1,25; 8,61</t>
+          <t>0,1; 7,11</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-3,75; 2,03</t>
+          <t>-3,74; 2,24</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,3; 6,69</t>
+          <t>-0,26; 5,83</t>
         </is>
       </c>
     </row>
@@ -754,7 +754,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>-17,59</t>
+          <t>-1,48</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -764,7 +764,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>0,15</t>
+          <t>-0,54</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -774,7 +774,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-9,99</t>
+          <t>-1,01</t>
         </is>
       </c>
     </row>
@@ -787,32 +787,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-4,04; 3,1</t>
+          <t>-4,3; 2,62</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-50,9; 0,57</t>
+          <t>-5,07; 2,5</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,31; 6,41</t>
+          <t>1,23; 6,46</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-2,78; 3,0</t>
+          <t>-3,42; 2,44</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-0,54; 3,84</t>
+          <t>-0,43; 3,86</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-35,09; 0,5</t>
+          <t>-3,45; 1,57</t>
         </is>
       </c>
     </row>
@@ -830,7 +830,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>-21,12%</t>
+          <t>-1,78%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -840,7 +840,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>-0,62%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -850,7 +850,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-11,64%</t>
+          <t>-1,17%</t>
         </is>
       </c>
     </row>
@@ -863,32 +863,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-4,76; 3,86</t>
+          <t>-5,02; 3,23</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-60,95; 0,69</t>
+          <t>-6,0; 3,07</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,46; 7,44</t>
+          <t>1,39; 7,42</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-3,07; 3,43</t>
+          <t>-3,81; 2,78</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-0,63; 4,52</t>
+          <t>-0,5; 4,57</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-40,55; 0,61</t>
+          <t>-3,95; 1,85</t>
         </is>
       </c>
     </row>
@@ -910,7 +910,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>-1,68</t>
+          <t>-2,32</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -920,7 +920,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>2,15</t>
+          <t>-0,05</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -930,7 +930,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0,83</t>
+          <t>-1,2</t>
         </is>
       </c>
     </row>
@@ -943,32 +943,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-5,51; 1,91</t>
+          <t>-5,47; 2,3</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-6,82; 2,87</t>
+          <t>-6,94; 2,36</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-1,98; 3,79</t>
+          <t>-1,84; 4,24</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-1,46; 7,16</t>
+          <t>-3,29; 2,96</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-2,91; 2,09</t>
+          <t>-2,58; 2,06</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-2,37; 5,66</t>
+          <t>-4,09; 1,3</t>
         </is>
       </c>
     </row>
@@ -986,7 +986,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>-1,97%</t>
+          <t>-2,72%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -996,7 +996,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>-0,05%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1006,7 +1006,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>-1,36%</t>
         </is>
       </c>
     </row>
@@ -1019,32 +1019,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-6,37; 2,14</t>
+          <t>-6,37; 2,76</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-7,93; 3,43</t>
+          <t>-8,07; 2,78</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-2,18; 4,24</t>
+          <t>-2,0; 4,8</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-1,65; 8,02</t>
+          <t>-3,58; 3,3</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-3,3; 2,43</t>
+          <t>-2,91; 2,38</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-2,67; 6,5</t>
+          <t>-4,61; 1,51</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>-5,49</t>
+          <t>-6,88</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -1076,7 +1076,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>-9,47</t>
+          <t>-5,46</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1086,7 +1086,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>-7,56</t>
+          <t>-6,11</t>
         </is>
       </c>
     </row>
@@ -1099,32 +1099,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-5,97; 0,76</t>
+          <t>-5,9; 1,0</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-9,75; -2,11</t>
+          <t>-10,68; -3,0</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-7,23; -1,5</t>
+          <t>-7,27; -1,81</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-24,52; -2,7</t>
+          <t>-8,45; -2,62</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-5,86; -1,4</t>
+          <t>-5,53; -1,25</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-17,31; -3,84</t>
+          <t>-8,36; -3,61</t>
         </is>
       </c>
     </row>
@@ -1142,7 +1142,7 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>-6,39%</t>
+          <t>-8,02%</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -1152,7 +1152,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>-10,4%</t>
+          <t>-6,0%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>-8,54%</t>
+          <t>-6,9%</t>
         </is>
       </c>
     </row>
@@ -1175,32 +1175,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-6,87; 0,91</t>
+          <t>-6,7; 1,26</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-11,18; -2,52</t>
+          <t>-12,31; -3,59</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-7,86; -1,67</t>
+          <t>-7,92; -2,03</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-26,86; -2,99</t>
+          <t>-9,13; -3,03</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-6,55; -1,61</t>
+          <t>-6,26; -1,42</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-19,35; -4,31</t>
+          <t>-9,36; -4,05</t>
         </is>
       </c>
     </row>
@@ -1222,7 +1222,7 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>-7,66</t>
+          <t>-2,63</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -1232,7 +1232,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>-1,43</t>
+          <t>-1,19</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1242,7 +1242,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>-4,44</t>
+          <t>-1,88</t>
         </is>
       </c>
     </row>
@@ -1255,32 +1255,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-3,55; 0,03</t>
+          <t>-3,52; -0,01</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-25,32; -1,13</t>
+          <t>-4,83; -0,7</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-1,36; 1,65</t>
+          <t>-1,29; 1,63</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-7,16; 1,1</t>
+          <t>-2,56; 0,49</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-1,83; 0,36</t>
+          <t>-1,9; 0,34</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-14,12; -0,77</t>
+          <t>-3,13; -0,66</t>
         </is>
       </c>
     </row>
@@ -1298,7 +1298,7 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>-8,97%</t>
+          <t>-3,08%</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>-1,6%</t>
+          <t>-1,33%</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -1318,7 +1318,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>-5,07%</t>
+          <t>-2,14%</t>
         </is>
       </c>
     </row>
@@ -1331,32 +1331,32 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-4,12; 0,03</t>
+          <t>-4,07; -0,02</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-29,6; -1,35</t>
+          <t>-5,64; -0,84</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-1,5; 1,85</t>
+          <t>-1,42; 1,82</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-7,99; 1,22</t>
+          <t>-2,83; 0,55</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-2,08; 0,41</t>
+          <t>-2,15; 0,39</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-16,3; -0,9</t>
+          <t>-3,56; -0,78</t>
         </is>
       </c>
     </row>
